--- a/listas_siesa.xlsx
+++ b/listas_siesa.xlsx
@@ -1890,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L1030"/>
@@ -5596,7 +5596,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
         <v>30</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>30</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
         <v>30</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>30</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
         <v>30</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
         <v>30</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>30</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
         <v>30</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
         <v>30</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>30</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
         <v>62</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
         <v>82</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
         <v>84</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
         <v>84</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
         <v>84</v>
       </c>
@@ -8674,7 +8674,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
         <v>84</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
         <v>84</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
         <v>86</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
         <v>88</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
         <v>89</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
         <v>90</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
         <v>91</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
         <v>95</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
         <v>96</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
         <v>96</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
         <v>96</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
         <v>96</v>
       </c>
@@ -9586,7 +9586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
         <v>96</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
         <v>96</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
         <v>96</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
         <v>96</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
         <v>96</v>
       </c>
@@ -9776,7 +9776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
         <v>96</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="s">
         <v>100</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
         <v>100</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="2" t="s">
         <v>100</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="s">
         <v>100</v>
       </c>
@@ -10954,7 +10954,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="s">
         <v>102</v>
       </c>
@@ -10992,7 +10992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
         <v>102</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
         <v>102</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
         <v>102</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="8" t="s">
         <v>103</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="8" t="s">
         <v>103</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="8" t="s">
         <v>103</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="8" t="s">
         <v>103</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="8" t="s">
         <v>103</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="8" t="s">
         <v>103</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="8" t="s">
         <v>103</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="8" t="s">
         <v>103</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="8" t="s">
         <v>103</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="8" t="s">
         <v>103</v>
       </c>
@@ -11486,7 +11486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="8" t="s">
         <v>103</v>
       </c>
@@ -11524,7 +11524,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="8" t="s">
         <v>103</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="8" t="s">
         <v>103</v>
       </c>
@@ -11600,7 +11600,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="8" t="s">
         <v>103</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="8" t="s">
         <v>103</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="8" t="s">
         <v>103</v>
       </c>
@@ -11714,7 +11714,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="8" t="s">
         <v>103</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="8" t="s">
         <v>103</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="2" t="s">
         <v>103</v>
       </c>
@@ -11828,7 +11828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="2" t="s">
         <v>103</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
         <v>103</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="2" t="s">
         <v>103</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="2" t="s">
         <v>103</v>
       </c>
@@ -11980,7 +11980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="2" t="s">
         <v>103</v>
       </c>
@@ -12018,7 +12018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="s">
         <v>103</v>
       </c>
@@ -12056,7 +12056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="2" t="s">
         <v>103</v>
       </c>
@@ -12094,7 +12094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="2" t="s">
         <v>103</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
         <v>103</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="2" t="s">
         <v>103</v>
       </c>
@@ -12208,7 +12208,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
         <v>103</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="2" t="s">
         <v>103</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="2" t="s">
         <v>103</v>
       </c>
@@ -12322,7 +12322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="2" t="s">
         <v>103</v>
       </c>
@@ -12360,7 +12360,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="2" t="s">
         <v>103</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="2" t="s">
         <v>103</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="2" t="s">
         <v>103</v>
       </c>
@@ -13348,7 +13348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="2" t="s">
         <v>113</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="2" t="s">
         <v>113</v>
       </c>
@@ -13424,7 +13424,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="2" t="s">
         <v>113</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="2" t="s">
         <v>116</v>
       </c>
@@ -14108,7 +14108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
         <v>116</v>
       </c>
@@ -14146,7 +14146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="2" t="s">
         <v>116</v>
       </c>
@@ -14184,7 +14184,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="2" t="s">
         <v>116</v>
       </c>
@@ -14222,7 +14222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="2" t="s">
         <v>116</v>
       </c>
@@ -14260,7 +14260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="2" t="s">
         <v>116</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="2" t="s">
         <v>116</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="2" t="s">
         <v>116</v>
       </c>
@@ -14374,7 +14374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="2" t="s">
         <v>116</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="2" t="s">
         <v>116</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="2" t="s">
         <v>116</v>
       </c>
@@ -14488,7 +14488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="2" t="s">
         <v>116</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="2" t="s">
         <v>116</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
         <v>116</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="2" t="s">
         <v>116</v>
       </c>
@@ -14640,7 +14640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="2" t="s">
         <v>116</v>
       </c>
@@ -14678,7 +14678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="2" t="s">
         <v>116</v>
       </c>
@@ -14716,7 +14716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="2" t="s">
         <v>116</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="2" t="s">
         <v>117</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="2" t="s">
         <v>117</v>
       </c>
@@ -14830,7 +14830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="2" t="s">
         <v>117</v>
       </c>
@@ -14868,7 +14868,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="2" t="s">
         <v>117</v>
       </c>
@@ -14906,7 +14906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="2" t="s">
         <v>117</v>
       </c>
@@ -14944,7 +14944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="2" t="s">
         <v>117</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="2" t="s">
         <v>117</v>
       </c>
@@ -15020,7 +15020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="2" t="s">
         <v>117</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="2" t="s">
         <v>117</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
         <v>117</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="2" t="s">
         <v>118</v>
       </c>
@@ -15172,7 +15172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="2" t="s">
         <v>118</v>
       </c>
@@ -15210,7 +15210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="2" t="s">
         <v>118</v>
       </c>
@@ -15248,7 +15248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="2" t="s">
         <v>118</v>
       </c>
@@ -17794,7 +17794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="12" t="s">
         <v>124</v>
       </c>
@@ -17832,7 +17832,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="12" t="s">
         <v>124</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="12" t="s">
         <v>124</v>
       </c>
@@ -17908,7 +17908,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="12" t="s">
         <v>124</v>
       </c>
@@ -17946,7 +17946,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="12" t="s">
         <v>124</v>
       </c>
@@ -18250,7 +18250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="2" t="s">
         <v>127</v>
       </c>
@@ -18288,7 +18288,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="s">
         <v>127</v>
       </c>
@@ -18326,7 +18326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="s">
         <v>127</v>
       </c>
@@ -18934,7 +18934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="2" t="s">
         <v>83</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="2" t="s">
         <v>83</v>
       </c>
@@ -19010,7 +19010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="2" t="s">
         <v>83</v>
       </c>
@@ -19048,7 +19048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="s">
         <v>83</v>
       </c>
@@ -19086,7 +19086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="s">
         <v>26</v>
       </c>
@@ -19124,7 +19124,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="s">
         <v>26</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="s">
         <v>26</v>
       </c>
@@ -19200,7 +19200,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="s">
         <v>26</v>
       </c>
@@ -19238,7 +19238,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="s">
         <v>137</v>
       </c>
@@ -20720,7 +20720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="2" t="s">
         <v>144</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="s">
         <v>144</v>
       </c>
@@ -20796,7 +20796,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="2" t="s">
         <v>144</v>
       </c>
@@ -21480,7 +21480,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="516" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="516" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="s">
         <v>149</v>
       </c>
@@ -21518,7 +21518,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="517" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
         <v>149</v>
       </c>
@@ -21556,7 +21556,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="518" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="2" t="s">
         <v>149</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="519" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="519" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="2" t="s">
         <v>143</v>
       </c>
@@ -21632,7 +21632,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="520" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="520" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="2" t="s">
         <v>143</v>
       </c>
@@ -21670,7 +21670,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="521" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="521" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="2" t="s">
         <v>52</v>
       </c>
@@ -21708,7 +21708,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="522" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="2" t="s">
         <v>52</v>
       </c>
@@ -21746,7 +21746,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="523" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="523" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="2" t="s">
         <v>52</v>
       </c>
@@ -21784,7 +21784,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="524" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="524" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="2" t="s">
         <v>93</v>
       </c>
@@ -21822,7 +21822,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="525" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="525" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="2" t="s">
         <v>93</v>
       </c>
@@ -21860,7 +21860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="2" t="s">
         <v>93</v>
       </c>
@@ -21898,7 +21898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="527" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="2" t="s">
         <v>120</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="528" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="528" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="2" t="s">
         <v>120</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="529" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="2" t="s">
         <v>120</v>
       </c>
@@ -22012,7 +22012,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="530" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="530" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="2" t="s">
         <v>120</v>
       </c>
@@ -22050,7 +22050,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="531" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="531" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="2" t="s">
         <v>120</v>
       </c>
@@ -22088,7 +22088,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="532" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="532" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="2" t="s">
         <v>120</v>
       </c>
@@ -22126,7 +22126,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="533" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="533" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="s">
         <v>157</v>
       </c>
@@ -22164,7 +22164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="534" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="534" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="2" t="s">
         <v>157</v>
       </c>
@@ -22202,7 +22202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="535" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="2" t="s">
         <v>157</v>
       </c>
@@ -22240,7 +22240,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="536" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="2" t="s">
         <v>157</v>
       </c>
@@ -22278,7 +22278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="537" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="2" t="s">
         <v>157</v>
       </c>
@@ -22316,7 +22316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="538" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="2" t="s">
         <v>157</v>
       </c>
@@ -22354,7 +22354,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="539" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="2" t="s">
         <v>157</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="540" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="540" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="2" t="s">
         <v>157</v>
       </c>
@@ -22430,7 +22430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="541" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="541" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="2" t="s">
         <v>157</v>
       </c>
@@ -22468,7 +22468,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="542" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="542" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="2" t="s">
         <v>157</v>
       </c>
@@ -22506,7 +22506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="543" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="543" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="2" t="s">
         <v>157</v>
       </c>
@@ -22544,7 +22544,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="544" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="544" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="2" t="s">
         <v>94</v>
       </c>
@@ -22582,7 +22582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="545" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="545" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="2" t="s">
         <v>94</v>
       </c>
@@ -22620,7 +22620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="546" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="546" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="2" t="s">
         <v>94</v>
       </c>
@@ -22924,7 +22924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="554" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="554" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="16" t="s">
         <v>161</v>
       </c>
@@ -22962,7 +22962,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="555" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="555" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="16" t="s">
         <v>161</v>
       </c>
@@ -23000,7 +23000,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="556" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="556" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="16" t="s">
         <v>161</v>
       </c>
@@ -23038,7 +23038,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="557" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="557" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="16" t="s">
         <v>161</v>
       </c>
@@ -26496,7 +26496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="648" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="648" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="2" t="s">
         <v>177</v>
       </c>
@@ -26534,7 +26534,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="649" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="649" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="2" t="s">
         <v>177</v>
       </c>
@@ -26572,7 +26572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="650" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="650" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="2" t="s">
         <v>177</v>
       </c>
@@ -26610,7 +26610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="651" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="651" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="2" t="s">
         <v>177</v>
       </c>
@@ -26648,7 +26648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="652" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="652" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="2" t="s">
         <v>177</v>
       </c>
@@ -26686,7 +26686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="653" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="653" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="2" t="s">
         <v>177</v>
       </c>
@@ -26724,7 +26724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="654" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="654" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="2" t="s">
         <v>177</v>
       </c>
@@ -26762,7 +26762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="655" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="655" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="2" t="s">
         <v>177</v>
       </c>
@@ -28016,7 +28016,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="688" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="688" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="16" t="s">
         <v>170</v>
       </c>
@@ -28054,7 +28054,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="689" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="689" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="2" t="s">
         <v>170</v>
       </c>
@@ -28092,7 +28092,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="690" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="690" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="2" t="s">
         <v>170</v>
       </c>
@@ -28130,7 +28130,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="691" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="691" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="2" t="s">
         <v>170</v>
       </c>
@@ -28168,7 +28168,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="692" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="692" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="2" t="s">
         <v>170</v>
       </c>
@@ -28586,7 +28586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="703" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="703" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="2" t="s">
         <v>53</v>
       </c>
@@ -28624,7 +28624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="704" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="704" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="2" t="s">
         <v>53</v>
       </c>
@@ -28662,7 +28662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="705" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="705" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="2" t="s">
         <v>53</v>
       </c>
@@ -28700,7 +28700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="706" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="706" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="2" t="s">
         <v>53</v>
       </c>
@@ -28738,7 +28738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="707" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="707" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="2" t="s">
         <v>53</v>
       </c>
@@ -28776,7 +28776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="708" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="708" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="2" t="s">
         <v>53</v>
       </c>
@@ -28814,7 +28814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="709" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="709" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="2" t="s">
         <v>53</v>
       </c>
@@ -28852,7 +28852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="710" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="710" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="2" t="s">
         <v>53</v>
       </c>
@@ -29498,7 +29498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="727" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="727" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="2" t="s">
         <v>191</v>
       </c>
@@ -29536,7 +29536,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="728" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="728" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="2" t="s">
         <v>191</v>
       </c>
@@ -29574,7 +29574,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="729" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="729" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="2" t="s">
         <v>121</v>
       </c>
@@ -29612,7 +29612,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="730" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="730" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="2" t="s">
         <v>121</v>
       </c>
@@ -29650,7 +29650,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="731" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="731" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="2" t="s">
         <v>121</v>
       </c>
@@ -29688,7 +29688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="732" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="732" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="2" t="s">
         <v>121</v>
       </c>
@@ -29726,7 +29726,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="733" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="733" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="2" t="s">
         <v>195</v>
       </c>
@@ -29764,7 +29764,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="734" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="734" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="2" t="s">
         <v>195</v>
       </c>
@@ -29802,7 +29802,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="735" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="735" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="2" t="s">
         <v>195</v>
       </c>
@@ -29840,7 +29840,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="736" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="736" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="2" t="s">
         <v>195</v>
       </c>
@@ -29878,7 +29878,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="737" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="737" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="2" t="s">
         <v>195</v>
       </c>
@@ -29916,7 +29916,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="738" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="738" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="2" t="s">
         <v>197</v>
       </c>
@@ -29954,7 +29954,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="739" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="739" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="2" t="s">
         <v>197</v>
       </c>
@@ -30220,7 +30220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="746" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="746" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="2" t="s">
         <v>192</v>
       </c>
@@ -30258,7 +30258,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="747" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="747" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="2" t="s">
         <v>192</v>
       </c>
@@ -30296,7 +30296,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="748" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="748" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="2" t="s">
         <v>196</v>
       </c>
@@ -30334,7 +30334,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="749" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="749" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="2" t="s">
         <v>196</v>
       </c>
@@ -30372,7 +30372,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="750" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="750" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="2" t="s">
         <v>196</v>
       </c>
@@ -30410,7 +30410,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="751" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="751" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="2" t="s">
         <v>196</v>
       </c>
@@ -30448,7 +30448,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="752" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="752" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="2" t="s">
         <v>175</v>
       </c>
@@ -30486,7 +30486,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="753" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="753" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="2" t="s">
         <v>175</v>
       </c>
@@ -30524,7 +30524,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="754" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="754" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="2" t="s">
         <v>175</v>
       </c>
@@ -30562,7 +30562,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="755" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="755" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="2" t="s">
         <v>175</v>
       </c>
@@ -30600,7 +30600,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="756" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="756" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="2" t="s">
         <v>175</v>
       </c>
@@ -31398,7 +31398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="777" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="777" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="2" t="s">
         <v>99</v>
       </c>
@@ -31436,7 +31436,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="778" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="778" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="2" t="s">
         <v>99</v>
       </c>
@@ -31474,7 +31474,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="779" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="779" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="2" t="s">
         <v>99</v>
       </c>
@@ -31512,7 +31512,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="780" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="780" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="2" t="s">
         <v>37</v>
       </c>
@@ -31550,7 +31550,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="781" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="781" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="2" t="s">
         <v>37</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="782" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="782" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="2" t="s">
         <v>37</v>
       </c>
@@ -31626,7 +31626,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="783" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="783" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="2" t="s">
         <v>37</v>
       </c>
@@ -31664,7 +31664,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="784" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="784" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="2" t="s">
         <v>37</v>
       </c>
@@ -31702,7 +31702,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="785" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="785" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="2" t="s">
         <v>37</v>
       </c>
@@ -31740,7 +31740,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="786" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="786" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="2" t="s">
         <v>37</v>
       </c>
@@ -31778,7 +31778,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="787" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="787" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="2" t="s">
         <v>37</v>
       </c>
@@ -31816,7 +31816,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="788" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="788" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="2" t="s">
         <v>37</v>
       </c>
@@ -31854,7 +31854,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="789" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="789" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="2" t="s">
         <v>37</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="790" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="790" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="2" t="s">
         <v>37</v>
       </c>
@@ -31930,7 +31930,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="791" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="791" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="2" t="s">
         <v>81</v>
       </c>
@@ -31968,7 +31968,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="792" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="792" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="2" t="s">
         <v>81</v>
       </c>
@@ -32006,7 +32006,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="793" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="793" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="2" t="s">
         <v>81</v>
       </c>
@@ -32044,7 +32044,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="794" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="794" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="2" t="s">
         <v>81</v>
       </c>
@@ -32082,7 +32082,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="795" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="795" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="2" t="s">
         <v>81</v>
       </c>
@@ -32120,7 +32120,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="796" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="796" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="2" t="s">
         <v>81</v>
       </c>
@@ -32158,7 +32158,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="797" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="797" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="2" t="s">
         <v>81</v>
       </c>
@@ -32196,7 +32196,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="798" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="798" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="2" t="s">
         <v>81</v>
       </c>
@@ -32234,7 +32234,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="799" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="799" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="2" t="s">
         <v>81</v>
       </c>
@@ -32272,7 +32272,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="800" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="800" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="2" t="s">
         <v>81</v>
       </c>
@@ -32310,7 +32310,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="801" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="801" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="2" t="s">
         <v>81</v>
       </c>
@@ -32348,7 +32348,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="802" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="802" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="2" t="s">
         <v>81</v>
       </c>
@@ -32386,7 +32386,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="803" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="803" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="2" t="s">
         <v>81</v>
       </c>
@@ -32424,7 +32424,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="804" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="804" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="2" t="s">
         <v>81</v>
       </c>
@@ -32462,7 +32462,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="805" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="805" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="2" t="s">
         <v>81</v>
       </c>
@@ -32500,7 +32500,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="806" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="806" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="2" t="s">
         <v>81</v>
       </c>
@@ -32538,7 +32538,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="807" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="807" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="2" t="s">
         <v>17</v>
       </c>
@@ -32576,7 +32576,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="808" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="808" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="2" t="s">
         <v>17</v>
       </c>
@@ -32614,7 +32614,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="809" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="809" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="2" t="s">
         <v>17</v>
       </c>
@@ -32652,7 +32652,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="810" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="810" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="2" t="s">
         <v>17</v>
       </c>
@@ -32690,7 +32690,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="811" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="811" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="2" t="s">
         <v>17</v>
       </c>
@@ -32728,7 +32728,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="812" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="812" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="2" t="s">
         <v>17</v>
       </c>
@@ -32766,7 +32766,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="813" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="813" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="2" t="s">
         <v>17</v>
       </c>
@@ -32804,7 +32804,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="814" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="814" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="2" t="s">
         <v>152</v>
       </c>
@@ -32842,7 +32842,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="815" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="815" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="2" t="s">
         <v>152</v>
       </c>
@@ -32880,7 +32880,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="816" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="816" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="2" t="s">
         <v>152</v>
       </c>
@@ -32918,7 +32918,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="817" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="817" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="2" t="s">
         <v>152</v>
       </c>
@@ -32956,7 +32956,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="818" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="818" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="2" t="s">
         <v>152</v>
       </c>
@@ -32994,7 +32994,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="819" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="819" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="2" t="s">
         <v>152</v>
       </c>
@@ -33032,7 +33032,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="820" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="820" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="2" t="s">
         <v>152</v>
       </c>
@@ -33070,7 +33070,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="821" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="821" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="2" t="s">
         <v>152</v>
       </c>
@@ -33108,7 +33108,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="822" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="822" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="2" t="s">
         <v>33</v>
       </c>
@@ -33146,7 +33146,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="823" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="823" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="2" t="s">
         <v>33</v>
       </c>
@@ -33184,7 +33184,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="824" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="824" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="2" t="s">
         <v>33</v>
       </c>
@@ -33222,7 +33222,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="825" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="825" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="2" t="s">
         <v>33</v>
       </c>
@@ -33526,7 +33526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="833" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="833" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="2" t="s">
         <v>210</v>
       </c>
@@ -33564,7 +33564,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="834" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="834" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="2" t="s">
         <v>210</v>
       </c>
@@ -33602,7 +33602,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="835" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="835" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="2" t="s">
         <v>210</v>
       </c>
@@ -33640,7 +33640,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="836" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="836" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="2" t="s">
         <v>211</v>
       </c>
@@ -33678,7 +33678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="837" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="837" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="2" t="s">
         <v>211</v>
       </c>
@@ -34134,7 +34134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="849" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="849" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="2" t="s">
         <v>171</v>
       </c>
@@ -34172,7 +34172,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="850" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="850" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="2" t="s">
         <v>171</v>
       </c>
@@ -34210,7 +34210,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="851" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="851" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="2" t="s">
         <v>171</v>
       </c>
@@ -34248,7 +34248,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="852" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="852" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="2" t="s">
         <v>171</v>
       </c>
@@ -34286,7 +34286,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="853" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="853" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="2" t="s">
         <v>171</v>
       </c>
@@ -34324,7 +34324,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="854" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="854" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="2" t="s">
         <v>171</v>
       </c>
@@ -36262,7 +36262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="905" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="905" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="2" t="s">
         <v>22</v>
       </c>
@@ -36300,7 +36300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="906" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="906" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="2" t="s">
         <v>22</v>
       </c>
@@ -36338,7 +36338,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="907" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="907" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="2" t="s">
         <v>22</v>
       </c>
@@ -36376,7 +36376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="908" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="908" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="2" t="s">
         <v>22</v>
       </c>
@@ -36414,7 +36414,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="909" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="909" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="2" t="s">
         <v>22</v>
       </c>
@@ -36452,7 +36452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="910" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="910" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="2" t="s">
         <v>63</v>
       </c>
@@ -36490,7 +36490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="911" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="911" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="2" t="s">
         <v>63</v>
       </c>
@@ -36528,7 +36528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="912" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="912" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="2" t="s">
         <v>63</v>
       </c>
@@ -36566,7 +36566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="913" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="913" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="2" t="s">
         <v>63</v>
       </c>
@@ -36604,7 +36604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="914" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="914" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="2" t="s">
         <v>63</v>
       </c>
@@ -36642,7 +36642,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="915" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="915" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="2" t="s">
         <v>63</v>
       </c>
@@ -36680,7 +36680,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="916" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="916" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="2" t="s">
         <v>63</v>
       </c>
@@ -36718,7 +36718,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="917" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="917" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="2" t="s">
         <v>63</v>
       </c>
@@ -36756,7 +36756,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="918" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="918" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="2" t="s">
         <v>63</v>
       </c>
@@ -36794,7 +36794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="919" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="919" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="2" t="s">
         <v>63</v>
       </c>
@@ -36832,7 +36832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="920" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="920" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="2" t="s">
         <v>63</v>
       </c>
@@ -36870,7 +36870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="921" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="921" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="2" t="s">
         <v>63</v>
       </c>
@@ -36908,7 +36908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="922" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="922" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="2" t="s">
         <v>221</v>
       </c>
@@ -36946,7 +36946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="923" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="923" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="2" t="s">
         <v>32</v>
       </c>
@@ -36984,7 +36984,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="924" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="924" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="2" t="s">
         <v>32</v>
       </c>
@@ -37022,7 +37022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="925" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="925" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="2" t="s">
         <v>32</v>
       </c>
@@ -37060,7 +37060,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="926" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="926" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="2" t="s">
         <v>32</v>
       </c>
@@ -37098,7 +37098,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="927" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="927" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="2" t="s">
         <v>32</v>
       </c>
@@ -37136,7 +37136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="928" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="928" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="2" t="s">
         <v>32</v>
       </c>
@@ -37174,7 +37174,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="929" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="929" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="2" t="s">
         <v>32</v>
       </c>
@@ -37212,7 +37212,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="930" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="930" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="2" t="s">
         <v>32</v>
       </c>
@@ -37250,7 +37250,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="931" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="931" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="2" t="s">
         <v>32</v>
       </c>
@@ -37288,7 +37288,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="932" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="932" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="2" t="s">
         <v>32</v>
       </c>
@@ -37326,7 +37326,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="933" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="933" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="2" t="s">
         <v>223</v>
       </c>
@@ -37364,7 +37364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="934" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="934" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="2" t="s">
         <v>224</v>
       </c>
@@ -37402,7 +37402,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="935" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="935" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="2" t="s">
         <v>224</v>
       </c>
@@ -37440,7 +37440,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="936" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="936" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="2" t="s">
         <v>224</v>
       </c>
@@ -37478,7 +37478,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="937" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="937" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="2" t="s">
         <v>224</v>
       </c>
@@ -37516,7 +37516,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="938" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="938" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="2" t="s">
         <v>224</v>
       </c>
@@ -37554,7 +37554,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="939" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="939" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="2" t="s">
         <v>224</v>
       </c>
@@ -37592,7 +37592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="940" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="940" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="2" t="s">
         <v>224</v>
       </c>
@@ -37630,7 +37630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="941" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="941" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="2" t="s">
         <v>224</v>
       </c>
@@ -37668,7 +37668,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="942" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="942" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="2" t="s">
         <v>224</v>
       </c>
@@ -37706,7 +37706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="943" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="943" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="2" t="s">
         <v>224</v>
       </c>
@@ -37744,7 +37744,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="944" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="944" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="2" t="s">
         <v>224</v>
       </c>
@@ -37782,7 +37782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="945" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="945" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="2" t="s">
         <v>224</v>
       </c>
@@ -37820,7 +37820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="946" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="946" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="2" t="s">
         <v>224</v>
       </c>
@@ -37858,7 +37858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="947" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="947" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="2" t="s">
         <v>224</v>
       </c>
@@ -37896,7 +37896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="948" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="948" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="2" t="s">
         <v>224</v>
       </c>
@@ -37934,7 +37934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="949" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="949" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="2" t="s">
         <v>226</v>
       </c>
@@ -37972,7 +37972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="950" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="950" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="2" t="s">
         <v>226</v>
       </c>
@@ -38010,7 +38010,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="951" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="951" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="2" t="s">
         <v>226</v>
       </c>
@@ -38048,7 +38048,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="952" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="952" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="2" t="s">
         <v>226</v>
       </c>
@@ -38086,7 +38086,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="953" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="953" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="2" t="s">
         <v>227</v>
       </c>
@@ -38124,7 +38124,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="954" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="954" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="2" t="s">
         <v>227</v>
       </c>
@@ -38162,7 +38162,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="955" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="955" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="2" t="s">
         <v>227</v>
       </c>
@@ -38200,7 +38200,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="956" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="956" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="2" t="s">
         <v>228</v>
       </c>
@@ -38238,7 +38238,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="957" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="957" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="2" t="s">
         <v>228</v>
       </c>
@@ -38276,7 +38276,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="958" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="958" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="2" t="s">
         <v>228</v>
       </c>
@@ -38314,7 +38314,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="959" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="959" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="2" t="s">
         <v>228</v>
       </c>
@@ -38352,7 +38352,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="960" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="960" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="2" t="s">
         <v>228</v>
       </c>
@@ -38390,7 +38390,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="961" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="961" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="2" t="s">
         <v>229</v>
       </c>
@@ -38428,7 +38428,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="962" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="962" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="2" t="s">
         <v>229</v>
       </c>
@@ -38466,7 +38466,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="963" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="963" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="2" t="s">
         <v>229</v>
       </c>
@@ -38504,7 +38504,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="964" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="964" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="2" t="s">
         <v>230</v>
       </c>
@@ -38542,7 +38542,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="965" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="965" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="2" t="s">
         <v>230</v>
       </c>
@@ -38580,7 +38580,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="966" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="966" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="2" t="s">
         <v>230</v>
       </c>
@@ -38618,7 +38618,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="967" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="967" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="2" t="s">
         <v>230</v>
       </c>
@@ -38656,7 +38656,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="968" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="968" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="2" t="s">
         <v>231</v>
       </c>
@@ -38694,7 +38694,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="969" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="969" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="2" t="s">
         <v>231</v>
       </c>
@@ -38732,7 +38732,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="970" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="970" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="2" t="s">
         <v>231</v>
       </c>
@@ -38770,7 +38770,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="971" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="971" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="2" t="s">
         <v>231</v>
       </c>
@@ -38808,7 +38808,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="972" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="972" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="2" t="s">
         <v>231</v>
       </c>
@@ -38846,7 +38846,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="973" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="973" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="2" t="s">
         <v>231</v>
       </c>
@@ -38884,7 +38884,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="974" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="974" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="2" t="s">
         <v>231</v>
       </c>
@@ -38922,7 +38922,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="975" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="975" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="2" t="s">
         <v>231</v>
       </c>
@@ -38960,7 +38960,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="976" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="976" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="2" t="s">
         <v>231</v>
       </c>
@@ -38998,7 +38998,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="977" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="977" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="2" t="s">
         <v>231</v>
       </c>
@@ -39036,7 +39036,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="978" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="978" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="2" t="s">
         <v>231</v>
       </c>
@@ -39074,7 +39074,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="979" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="979" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="2" t="s">
         <v>232</v>
       </c>
@@ -39112,7 +39112,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="980" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="980" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="2" t="s">
         <v>232</v>
       </c>
@@ -39150,7 +39150,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="981" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="981" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="2" t="s">
         <v>232</v>
       </c>
@@ -39188,7 +39188,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="982" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="982" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="2" t="s">
         <v>232</v>
       </c>
@@ -39226,7 +39226,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="983" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="983" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="2" t="s">
         <v>232</v>
       </c>
@@ -39264,7 +39264,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="984" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="984" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="2" t="s">
         <v>232</v>
       </c>
@@ -39302,7 +39302,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="985" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="985" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="2" t="s">
         <v>233</v>
       </c>
@@ -39340,7 +39340,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="986" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="986" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="2" t="s">
         <v>233</v>
       </c>
@@ -39378,7 +39378,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="987" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="987" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="2" t="s">
         <v>233</v>
       </c>
@@ -39416,7 +39416,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="988" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="988" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="2" t="s">
         <v>233</v>
       </c>
@@ -39454,7 +39454,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="989" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="989" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="2" t="s">
         <v>233</v>
       </c>
@@ -39492,7 +39492,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="990" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="990" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="2" t="s">
         <v>233</v>
       </c>
@@ -39530,7 +39530,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="991" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="991" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="2" t="s">
         <v>233</v>
       </c>
@@ -39568,7 +39568,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="992" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="992" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="2" t="s">
         <v>233</v>
       </c>
@@ -39606,7 +39606,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="993" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="993" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="2" t="s">
         <v>234</v>
       </c>
@@ -39644,7 +39644,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="994" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="994" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="2" t="s">
         <v>234</v>
       </c>
@@ -39682,7 +39682,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="995" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="995" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="2" t="s">
         <v>234</v>
       </c>
@@ -39720,7 +39720,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="996" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="996" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="2" t="s">
         <v>234</v>
       </c>
@@ -39758,7 +39758,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="997" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="997" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="2" t="s">
         <v>234</v>
       </c>
@@ -39796,7 +39796,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="998" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="998" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="2" t="s">
         <v>235</v>
       </c>
@@ -39834,7 +39834,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="999" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="999" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="2" t="s">
         <v>235</v>
       </c>
@@ -39872,7 +39872,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1000" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1000" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="2" t="s">
         <v>235</v>
       </c>
@@ -39910,7 +39910,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1001" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1001" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1001" s="2" t="s">
         <v>235</v>
       </c>
@@ -39948,7 +39948,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1002" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1002" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1002" s="2" t="s">
         <v>236</v>
       </c>
@@ -39986,7 +39986,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1003" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1003" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1003" s="2" t="s">
         <v>236</v>
       </c>
@@ -40024,7 +40024,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1004" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1004" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1004" s="2" t="s">
         <v>236</v>
       </c>
@@ -40062,7 +40062,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1005" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1005" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1005" s="2" t="s">
         <v>236</v>
       </c>
@@ -40100,7 +40100,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1006" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1006" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1006" s="2" t="s">
         <v>236</v>
       </c>
@@ -40138,7 +40138,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1007" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1007" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1007" s="2" t="s">
         <v>237</v>
       </c>
@@ -40176,7 +40176,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1008" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1008" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1008" s="2" t="s">
         <v>237</v>
       </c>
@@ -40214,7 +40214,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1009" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1009" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1009" s="2" t="s">
         <v>237</v>
       </c>
@@ -40252,7 +40252,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1010" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1010" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1010" s="2" t="s">
         <v>237</v>
       </c>
@@ -40290,7 +40290,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1011" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1011" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1011" s="2" t="s">
         <v>237</v>
       </c>
@@ -40328,7 +40328,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1012" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1012" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1012" s="2" t="s">
         <v>237</v>
       </c>
@@ -40366,7 +40366,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1013" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1013" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1013" s="2" t="s">
         <v>237</v>
       </c>
@@ -40404,7 +40404,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1014" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1014" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1014" s="2" t="s">
         <v>237</v>
       </c>
@@ -40442,7 +40442,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1015" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1015" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1015" s="2" t="s">
         <v>238</v>
       </c>
@@ -40480,7 +40480,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1016" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1016" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1016" s="2" t="s">
         <v>238</v>
       </c>
@@ -40518,7 +40518,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1017" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1017" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1017" s="2" t="s">
         <v>238</v>
       </c>
@@ -40556,7 +40556,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1018" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1018" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1018" s="2" t="s">
         <v>238</v>
       </c>
@@ -40594,7 +40594,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1019" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1019" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1019" s="2" t="s">
         <v>238</v>
       </c>
@@ -40632,7 +40632,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1020" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1020" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1020" s="2" t="s">
         <v>238</v>
       </c>
@@ -40670,7 +40670,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1021" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1021" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1021" s="2" t="s">
         <v>238</v>
       </c>
@@ -40708,7 +40708,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1022" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1022" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1022" s="2" t="s">
         <v>238</v>
       </c>
@@ -40746,7 +40746,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1023" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1023" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1023" s="2" t="s">
         <v>239</v>
       </c>
@@ -40784,7 +40784,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1024" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1024" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1024" s="2" t="s">
         <v>239</v>
       </c>
@@ -40822,7 +40822,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1025" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1025" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1025" s="2" t="s">
         <v>239</v>
       </c>
@@ -40860,7 +40860,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1026" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1026" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1026" s="2" t="s">
         <v>239</v>
       </c>
@@ -40898,7 +40898,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1027" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1027" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1027" s="2" t="s">
         <v>239</v>
       </c>
@@ -40936,7 +40936,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1028" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1028" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1028" s="2" t="s">
         <v>239</v>
       </c>
@@ -40974,7 +40974,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1029" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1029" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1029" s="2" t="s">
         <v>239</v>
       </c>
@@ -41012,7 +41012,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="1030" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1030" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1030" s="2" t="s">
         <v>239</v>
       </c>
@@ -41051,13 +41051,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1030">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="MF"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L1030"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
